--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -388,7 +388,7 @@
     <t>52</t>
   </si>
   <si>
-    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
+    <t>Autorisation par l'ARS pour la sous-traitance de préparation pharmaceutique présentant un risque pour la santé</t>
   </si>
   <si>
     <t>53</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260928120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -407,6 +407,18 @@
   </si>
   <si>
     <t>Accréditation par la Société Française de Recherche en Médecine du Sommeil (SFRMS)</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Centre expert pied diabétique</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>Centre expert Epileptologie</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R344-NiveauExpertise/FHIR/TRE-R344-NiveauExpertise</t>
@@ -741,7 +753,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1126,18 +1138,34 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>36</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B49" t="s" s="2">
-        <v>131</v>
+      <c r="B51" t="s" s="2">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
